--- a/correlation_analysis/benchmark_correlation_Qwen_2_5-3B.xlsx
+++ b/correlation_analysis/benchmark_correlation_Qwen_2_5-3B.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DLAMA</t>
+          <t>GeoMLAMA</t>
         </is>
       </c>
     </row>
@@ -456,10 +456,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8954678302795421</v>
+        <v>0.8335573280194482</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09471496541971769</v>
+        <v>0.850348667592647</v>
       </c>
     </row>
     <row r="3">
@@ -469,26 +469,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8954678302795421</v>
+        <v>0.8335573280194482</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2439057664869091</v>
+        <v>0.5070710398212707</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>DLAMA</t>
+          <t>GeoMLAMA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09471496541971769</v>
+        <v>0.850348667592647</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.2439057664869091</v>
+        <v>0.5070710398212707</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -521,7 +521,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DLAMA</t>
+          <t>GeoMLAMA</t>
         </is>
       </c>
     </row>
@@ -535,10 +535,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0158193515828794</v>
+        <v>0.1664426719805518</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8583523922805856</v>
+        <v>0.149651332407353</v>
       </c>
     </row>
     <row r="3">
@@ -548,26 +548,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0158193515828794</v>
+        <v>0.1664426719805518</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6413963300896284</v>
+        <v>0.4929289601787294</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>DLAMA</t>
+          <t>GeoMLAMA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8583523922805856</v>
+        <v>0.149651332407353</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6413963300896284</v>
+        <v>0.4929289601787294</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>

--- a/correlation_analysis/benchmark_correlation_Qwen_2_5-3B.xlsx
+++ b/correlation_analysis/benchmark_correlation_Qwen_2_5-3B.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>GeoMLAMA</t>
+          <t>DLAMA</t>
         </is>
       </c>
     </row>
@@ -456,10 +456,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8335573280194482</v>
+        <v>0.8954678302795421</v>
       </c>
       <c r="D2" t="n">
-        <v>0.850348667592647</v>
+        <v>0.2640072884947033</v>
       </c>
     </row>
     <row r="3">
@@ -469,26 +469,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8335573280194482</v>
+        <v>0.8954678302795421</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5070710398212707</v>
+        <v>-0.1437080716697182</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GeoMLAMA</t>
+          <t>DLAMA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.850348667592647</v>
+        <v>0.2640072884947033</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5070710398212707</v>
+        <v>-0.1437080716697182</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -521,7 +521,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>GeoMLAMA</t>
+          <t>DLAMA</t>
         </is>
       </c>
     </row>
@@ -535,10 +535,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1664426719805518</v>
+        <v>0.0158193515828794</v>
       </c>
       <c r="D2" t="n">
-        <v>0.149651332407353</v>
+        <v>0.6131897012473718</v>
       </c>
     </row>
     <row r="3">
@@ -548,26 +548,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1664426719805518</v>
+        <v>0.0158193515828794</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4929289601787294</v>
+        <v>0.7859218227521825</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GeoMLAMA</t>
+          <t>DLAMA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.149651332407353</v>
+        <v>0.6131897012473718</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4929289601787294</v>
+        <v>0.7859218227521825</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
